--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09FC2F1-00C6-4ECC-A8D6-480DFC32C558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F3662E-187B-40AA-96CA-759E11C97F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="367">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1096,6 +1096,48 @@
   </si>
   <si>
     <t>HH0640</t>
+  </si>
+  <si>
+    <t>Tiên Tân</t>
+  </si>
+  <si>
+    <t>HH007047</t>
+  </si>
+  <si>
+    <t>HH009-006</t>
+  </si>
+  <si>
+    <t>HH050-040</t>
+  </si>
+  <si>
+    <t>KDNL183</t>
+  </si>
+  <si>
+    <t>KDNL083</t>
+  </si>
+  <si>
+    <t>1K26TAE</t>
+  </si>
+  <si>
+    <t>Châu Sơn</t>
+  </si>
+  <si>
+    <t>KDNL182</t>
+  </si>
+  <si>
+    <t>1K26TCS</t>
+  </si>
+  <si>
+    <t>KDNL082</t>
+  </si>
+  <si>
+    <t>HH007046</t>
+  </si>
+  <si>
+    <t>HH009-005</t>
+  </si>
+  <si>
+    <t>HH050-039</t>
   </si>
 </sst>
 </file>
@@ -3050,6 +3092,30 @@
         <v>131111</v>
       </c>
       <c r="C44" s="10"/>
+      <c r="D44" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="45" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
@@ -3059,6 +3125,30 @@
         <v>131112</v>
       </c>
       <c r="C45" s="10"/>
+      <c r="D45" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F3662E-187B-40AA-96CA-759E11C97F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431A524F-16E6-42C1-A525-52C96846DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1900,9 +1900,6 @@
       <c r="A10" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="6">
-        <v>1000</v>
-      </c>
       <c r="D10" s="4" t="s">
         <v>40</v>
       </c>
@@ -1937,9 +1934,6 @@
       <c r="A11" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B11" s="6">
-        <v>1900</v>
-      </c>
       <c r="D11" s="5" t="s">
         <v>44</v>
       </c>
@@ -1973,9 +1967,6 @@
       <c r="A12" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B12" s="6">
-        <v>2000</v>
-      </c>
       <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
@@ -2008,9 +1999,6 @@
     <row r="13" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="B13" s="6">
-        <v>1000</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>53</v>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431A524F-16E6-42C1-A525-52C96846DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93366DB7-241F-4147-8B51-7B00052ADBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="371">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1138,6 +1138,18 @@
   </si>
   <si>
     <t>HH050-039</t>
+  </si>
+  <si>
+    <t>Quất Lâm</t>
+  </si>
+  <si>
+    <t>KDNL081</t>
+  </si>
+  <si>
+    <t>1K26TQL</t>
+  </si>
+  <si>
+    <t>KKKNT</t>
   </si>
 </sst>
 </file>
@@ -1900,6 +1912,9 @@
       <c r="A10" s="6" t="s">
         <v>223</v>
       </c>
+      <c r="B10" s="6">
+        <v>0</v>
+      </c>
       <c r="D10" s="4" t="s">
         <v>40</v>
       </c>
@@ -1934,6 +1949,9 @@
       <c r="A11" s="6" t="s">
         <v>224</v>
       </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
       <c r="D11" s="5" t="s">
         <v>44</v>
       </c>
@@ -1967,6 +1985,9 @@
       <c r="A12" s="6" t="s">
         <v>225</v>
       </c>
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
       <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
@@ -1999,6 +2020,9 @@
     <row r="13" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>222</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>53</v>
@@ -2288,8 +2312,8 @@
       <c r="A22" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="1">
-        <v>8</v>
+      <c r="B22" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>98</v>
@@ -3146,6 +3170,21 @@
         <v>131114</v>
       </c>
       <c r="C46" s="10"/>
+      <c r="D46" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93366DB7-241F-4147-8B51-7B00052ADBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ECD006-0A2A-4312-B00D-DE5F7568DECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="419">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1150,6 +1150,150 @@
   </si>
   <si>
     <t>KKKNT</t>
+  </si>
+  <si>
+    <t>HH007048</t>
+  </si>
+  <si>
+    <t>HH009-007</t>
+  </si>
+  <si>
+    <t>HH050-041</t>
+  </si>
+  <si>
+    <t>HH0643</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON95 Mức 3</t>
+  </si>
+  <si>
+    <t>HH051-034</t>
+  </si>
+  <si>
+    <t>HH051-012</t>
+  </si>
+  <si>
+    <t>HH051-013</t>
+  </si>
+  <si>
+    <t>HH051-032</t>
+  </si>
+  <si>
+    <t>HH051-007</t>
+  </si>
+  <si>
+    <t>HH051-026</t>
+  </si>
+  <si>
+    <t>HH051-036</t>
+  </si>
+  <si>
+    <t>HH051-014</t>
+  </si>
+  <si>
+    <t>HH051-019</t>
+  </si>
+  <si>
+    <t>HH051-002</t>
+  </si>
+  <si>
+    <t>HH051-020</t>
+  </si>
+  <si>
+    <t>HH051-028</t>
+  </si>
+  <si>
+    <t>HH051-025</t>
+  </si>
+  <si>
+    <t>HH051-003</t>
+  </si>
+  <si>
+    <t>HH051-009</t>
+  </si>
+  <si>
+    <t>HH051-022</t>
+  </si>
+  <si>
+    <t>HH051-018</t>
+  </si>
+  <si>
+    <t>HH051-011</t>
+  </si>
+  <si>
+    <t>HH051-008</t>
+  </si>
+  <si>
+    <t>HH051-001</t>
+  </si>
+  <si>
+    <t>HH051-017</t>
+  </si>
+  <si>
+    <t>HH051-015</t>
+  </si>
+  <si>
+    <t>HH051-024</t>
+  </si>
+  <si>
+    <t>HH051-006</t>
+  </si>
+  <si>
+    <t>HH051-029</t>
+  </si>
+  <si>
+    <t>HH051-004</t>
+  </si>
+  <si>
+    <t>HH051-031</t>
+  </si>
+  <si>
+    <t>HH051-021</t>
+  </si>
+  <si>
+    <t>HH051-027</t>
+  </si>
+  <si>
+    <t>HH051-033</t>
+  </si>
+  <si>
+    <t>HH051-005</t>
+  </si>
+  <si>
+    <t>HH051-023</t>
+  </si>
+  <si>
+    <t>HH051-030</t>
+  </si>
+  <si>
+    <t>HH051-035</t>
+  </si>
+  <si>
+    <t>HH051-037</t>
+  </si>
+  <si>
+    <t>HH051-016</t>
+  </si>
+  <si>
+    <t>HH051-038</t>
+  </si>
+  <si>
+    <t>HH051-039</t>
+  </si>
+  <si>
+    <t>HH051-040</t>
+  </si>
+  <si>
+    <t>HH051-041</t>
+  </si>
+  <si>
+    <t>HH051-045</t>
+  </si>
+  <si>
+    <t>HH051-044</t>
+  </si>
+  <si>
+    <t>HH051-042</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1782,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P55"/>
+  <dimension ref="A2:Q55"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1648,12 +1792,13 @@
     <col min="6" max="6" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
-    <col min="10" max="390" width="8.42578125" style="1" customWidth="1"/>
-    <col min="391" max="16384" width="8.42578125" style="1"/>
+    <col min="9" max="9" width="12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="1" customWidth="1"/>
+    <col min="11" max="391" width="8.42578125" style="1" customWidth="1"/>
+    <col min="392" max="16384" width="8.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="1" t="s">
         <v>224</v>
       </c>
@@ -1667,29 +1812,32 @@
         <v>222</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>224</v>
       </c>
@@ -1712,22 +1860,25 @@
         <v>283</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>225</v>
       </c>
@@ -1747,22 +1898,25 @@
         <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>223</v>
       </c>
@@ -1782,28 +1936,32 @@
         <v>21</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>222</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
@@ -1819,25 +1977,29 @@
       <c r="H7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="1"/>
       <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
@@ -1854,27 +2016,31 @@
         <v>33</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="4" t="s">
         <v>36</v>
       </c>
@@ -1890,31 +2056,35 @@
       <c r="H9" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>223</v>
       </c>
       <c r="B10" s="6">
         <v>0</v>
       </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="4" t="s">
         <v>40</v>
       </c>
@@ -1927,31 +2097,35 @@
       <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>224</v>
       </c>
       <c r="B11" s="6">
         <v>0</v>
       </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="5" t="s">
         <v>44</v>
       </c>
@@ -1964,30 +2138,34 @@
       <c r="G11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>225</v>
       </c>
       <c r="B12" s="6">
         <v>0</v>
       </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
@@ -2000,30 +2178,34 @@
       <c r="G12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>222</v>
       </c>
       <c r="B13" s="6">
         <v>0</v>
       </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
@@ -2036,24 +2218,33 @@
       <c r="G13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
       <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
@@ -2069,24 +2260,27 @@
       <c r="H14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="K14" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="L14" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="4" t="s">
         <v>63</v>
       </c>
@@ -2103,22 +2297,25 @@
         <v>67</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="D16" s="4" t="s">
         <v>68</v>
@@ -2133,22 +2330,25 @@
         <v>71</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="4" t="s">
         <v>72</v>
       </c>
@@ -2165,22 +2365,25 @@
         <v>76</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="4" t="s">
         <v>77</v>
       </c>
@@ -2197,22 +2400,25 @@
         <v>276</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="4" t="s">
         <v>81</v>
       </c>
@@ -2229,22 +2435,25 @@
         <v>85</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="4" t="s">
         <v>86</v>
       </c>
@@ -2261,22 +2470,25 @@
         <v>90</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="4" t="s">
         <v>92</v>
       </c>
@@ -2293,22 +2505,25 @@
         <v>279</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>97</v>
       </c>
@@ -2331,22 +2546,25 @@
         <v>277</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="4" t="s">
         <v>102</v>
       </c>
@@ -2363,22 +2581,25 @@
         <v>106</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
         <v>108</v>
       </c>
@@ -2395,22 +2616,25 @@
         <v>280</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="4" t="s">
         <v>113</v>
       </c>
@@ -2426,28 +2650,30 @@
       <c r="H25" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>117</v>
       </c>
       <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
       <c r="D26" s="4" t="s">
         <v>118</v>
       </c>
@@ -2464,26 +2690,28 @@
         <v>232</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
       <c r="D27" s="4" t="s">
         <v>122</v>
       </c>
@@ -2497,27 +2725,29 @@
         <v>125</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>126</v>
       </c>
       <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
       <c r="D28" s="4" t="s">
         <v>127</v>
       </c>
@@ -2531,29 +2761,31 @@
         <v>130</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B29" s="10">
         <v>131111</v>
       </c>
-      <c r="C29" s="10"/>
       <c r="D29" s="4" t="s">
         <v>131</v>
       </c>
@@ -2570,29 +2802,31 @@
         <v>135</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="10">
         <v>131112</v>
       </c>
-      <c r="C30" s="10"/>
       <c r="D30" s="4" t="s">
         <v>136</v>
       </c>
@@ -2609,29 +2843,31 @@
         <v>347</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="10">
         <v>131114</v>
       </c>
-      <c r="C31" s="10"/>
       <c r="D31" s="4" t="s">
         <v>140</v>
       </c>
@@ -2648,27 +2884,29 @@
         <v>144</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>219</v>
       </c>
       <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
       <c r="D32" s="4" t="s">
         <v>146</v>
       </c>
@@ -2685,29 +2923,31 @@
         <v>150</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="10">
         <v>51111</v>
       </c>
-      <c r="C33" s="10"/>
       <c r="D33" s="4" t="s">
         <v>151</v>
       </c>
@@ -2721,29 +2961,31 @@
         <v>154</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="10">
         <v>51115</v>
       </c>
-      <c r="C34" s="10"/>
       <c r="D34" s="4" t="s">
         <v>155</v>
       </c>
@@ -2757,29 +2999,31 @@
         <v>158</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="10">
         <v>51112</v>
       </c>
-      <c r="C35" s="10"/>
       <c r="D35" s="4" t="s">
         <v>159</v>
       </c>
@@ -2793,29 +3037,31 @@
         <v>162</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>220</v>
       </c>
       <c r="B36" s="10">
         <v>63211</v>
       </c>
-      <c r="C36" s="10"/>
       <c r="D36" s="4" t="s">
         <v>164</v>
       </c>
@@ -2829,27 +3075,29 @@
         <v>167</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="K36" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
       <c r="D37" s="4" t="s">
         <v>169</v>
       </c>
@@ -2866,29 +3114,31 @@
         <v>278</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B38" s="10">
         <v>333111</v>
       </c>
-      <c r="C38" s="10"/>
       <c r="D38" s="4" t="s">
         <v>173</v>
       </c>
@@ -2905,29 +3155,31 @@
         <v>284</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B39" s="10">
         <v>333112</v>
       </c>
-      <c r="C39" s="10"/>
       <c r="D39" s="4" t="s">
         <v>177</v>
       </c>
@@ -2944,29 +3196,31 @@
         <v>281</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="10">
         <v>333115</v>
       </c>
-      <c r="C40" s="10"/>
       <c r="D40" s="4" t="s">
         <v>285</v>
       </c>
@@ -2981,25 +3235,27 @@
         <v>290</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
       <c r="D41" s="1" t="s">
         <v>292</v>
       </c>
@@ -3013,27 +3269,29 @@
         <v>297</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>181</v>
       </c>
       <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
       <c r="D42" s="1" t="s">
         <v>299</v>
       </c>
@@ -3047,27 +3305,29 @@
         <v>304</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="K42" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>126</v>
       </c>
       <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
       <c r="D43" s="1" t="s">
         <v>345</v>
       </c>
@@ -3081,29 +3341,31 @@
         <v>349</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="K43" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B44" s="10">
         <v>131111</v>
       </c>
-      <c r="C44" s="10"/>
       <c r="D44" s="1" t="s">
         <v>353</v>
       </c>
@@ -3116,27 +3378,29 @@
       <c r="H44" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="I44" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B45" s="10">
         <v>131112</v>
       </c>
-      <c r="C45" s="10"/>
       <c r="D45" s="1" t="s">
         <v>360</v>
       </c>
@@ -3149,119 +3413,127 @@
       <c r="H45" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="I45" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="10">
         <v>131114</v>
       </c>
-      <c r="C46" s="10"/>
       <c r="D46" s="1" t="s">
         <v>367</v>
       </c>
+      <c r="F46" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>418</v>
+      </c>
       <c r="J46" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
         <v>221</v>
       </c>
       <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-    </row>
-    <row r="48" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B48" s="10">
         <v>3338111</v>
       </c>
-      <c r="C48" s="10"/>
-    </row>
-    <row r="49" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B49" s="10">
         <v>3338121</v>
       </c>
-      <c r="C49" s="10"/>
-    </row>
-    <row r="50" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B50" s="10">
         <v>333814</v>
       </c>
-      <c r="C50" s="10"/>
-    </row>
-    <row r="51" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
         <v>220</v>
       </c>
       <c r="B51" s="10">
         <v>63211</v>
       </c>
-      <c r="C51" s="10"/>
-    </row>
-    <row r="52" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B53" s="10">
         <v>333111</v>
       </c>
-      <c r="C53" s="10"/>
-    </row>
-    <row r="54" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B54" s="10">
         <v>333112</v>
       </c>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="10">
         <v>333115</v>
       </c>
-      <c r="C55" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ECD006-0A2A-4312-B00D-DE5F7568DECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D90DE3F-F230-4120-B389-B5D3B07BD0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="421">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1294,6 +1294,12 @@
   </si>
   <si>
     <t>HH051-042</t>
+  </si>
+  <si>
+    <t>HH0641</t>
+  </si>
+  <si>
+    <t>HH0642</t>
   </si>
 </sst>
 </file>
@@ -3381,6 +3387,9 @@
       <c r="I44" s="1" t="s">
         <v>416</v>
       </c>
+      <c r="J44" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="K44" s="1" t="s">
         <v>357</v>
       </c>
@@ -3415,6 +3424,9 @@
       </c>
       <c r="I45" s="1" t="s">
         <v>417</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>361</v>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D90DE3F-F230-4120-B389-B5D3B07BD0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A555939-9953-4751-A783-F63116A950F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="445">
   <si>
     <t>Mã kho</t>
   </si>
@@ -1300,6 +1300,78 @@
   </si>
   <si>
     <t>HH0642</t>
+  </si>
+  <si>
+    <t>Thiên Tôn</t>
+  </si>
+  <si>
+    <t>KDNL184</t>
+  </si>
+  <si>
+    <t>KDNL084</t>
+  </si>
+  <si>
+    <t>1K26TAG</t>
+  </si>
+  <si>
+    <t>HH009-009</t>
+  </si>
+  <si>
+    <t>HH050-044</t>
+  </si>
+  <si>
+    <t>HH051-047</t>
+  </si>
+  <si>
+    <t>KDNL181</t>
+  </si>
+  <si>
+    <t>Hợp Hưng</t>
+  </si>
+  <si>
+    <t>Trường Thi</t>
+  </si>
+  <si>
+    <t>KDNL185</t>
+  </si>
+  <si>
+    <t>KDNL186</t>
+  </si>
+  <si>
+    <t>KDNL085</t>
+  </si>
+  <si>
+    <t>KDNL086</t>
+  </si>
+  <si>
+    <t>1K26THH</t>
+  </si>
+  <si>
+    <t>1K26THI</t>
+  </si>
+  <si>
+    <t>HH009-010</t>
+  </si>
+  <si>
+    <t>HH050-045</t>
+  </si>
+  <si>
+    <t>HH051-048</t>
+  </si>
+  <si>
+    <t>HH0645</t>
+  </si>
+  <si>
+    <t>HH009-011</t>
+  </si>
+  <si>
+    <t>HH050-046</t>
+  </si>
+  <si>
+    <t>HH051-050</t>
+  </si>
+  <si>
+    <t>HH0646</t>
   </si>
 </sst>
 </file>
@@ -3467,7 +3539,7 @@
         <v>374</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>369</v>
@@ -3484,6 +3556,30 @@
         <v>221</v>
       </c>
       <c r="B47" s="10"/>
+      <c r="D47" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
@@ -3492,16 +3588,70 @@
       <c r="B48" s="10">
         <v>3338111</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D48" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B49" s="10">
         <v>3338121</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D49" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>11</v>
       </c>
@@ -3509,7 +3659,7 @@
         <v>333814</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
         <v>220</v>
       </c>
@@ -3517,13 +3667,13 @@
         <v>63211</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B52" s="10"/>
     </row>
-    <row r="53" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
         <v>18</v>
       </c>
@@ -3531,7 +3681,7 @@
         <v>333111</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
         <v>34</v>
       </c>
@@ -3539,7 +3689,7 @@
         <v>333112</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
         <v>11</v>
       </c>

--- a/Data_HDDT.xlsx
+++ b/Data_HDDT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A555939-9953-4751-A783-F63116A950F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C87EF8-F5E1-4E92-8AC9-78784AF4E205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1224,9 +1224,6 @@
     <t>HH051-008</t>
   </si>
   <si>
-    <t>HH051-001</t>
-  </si>
-  <si>
     <t>HH051-017</t>
   </si>
   <si>
@@ -1372,6 +1369,9 @@
   </si>
   <si>
     <t>HH0646</t>
+  </si>
+  <si>
+    <t>HH051-010</t>
   </si>
 </sst>
 </file>
@@ -2659,7 +2659,7 @@
         <v>106</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>190</v>
@@ -2694,7 +2694,7 @@
         <v>280</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>199</v>
@@ -2729,7 +2729,7 @@
         <v>275</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>198</v>
@@ -2768,7 +2768,7 @@
         <v>232</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>213</v>
@@ -2803,7 +2803,7 @@
         <v>125</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>211</v>
@@ -2839,7 +2839,7 @@
         <v>130</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>212</v>
@@ -2880,7 +2880,7 @@
         <v>135</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>214</v>
@@ -2921,7 +2921,7 @@
         <v>347</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>204</v>
@@ -2962,7 +2962,7 @@
         <v>144</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>186</v>
@@ -3001,7 +3001,7 @@
         <v>150</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>215</v>
@@ -3039,7 +3039,7 @@
         <v>154</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>206</v>
@@ -3077,7 +3077,7 @@
         <v>158</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>216</v>
@@ -3115,7 +3115,7 @@
         <v>162</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>195</v>
@@ -3153,7 +3153,7 @@
         <v>167</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>203</v>
@@ -3192,7 +3192,7 @@
         <v>278</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>184</v>
@@ -3233,7 +3233,7 @@
         <v>284</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>218</v>
@@ -3274,7 +3274,7 @@
         <v>281</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>201</v>
@@ -3313,7 +3313,7 @@
         <v>290</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>291</v>
@@ -3347,7 +3347,7 @@
         <v>297</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>298</v>
@@ -3383,7 +3383,7 @@
         <v>304</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>305</v>
@@ -3419,7 +3419,7 @@
         <v>349</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>352</v>
@@ -3457,10 +3457,10 @@
         <v>356</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>357</v>
@@ -3495,10 +3495,10 @@
         <v>366</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>361</v>
@@ -3533,13 +3533,13 @@
         <v>373</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>374</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>369</v>
@@ -3557,28 +3557,28 @@
       </c>
       <c r="B47" s="10"/>
       <c r="D47" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3589,31 +3589,31 @@
         <v>3338111</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
@@ -3624,31 +3624,31 @@
         <v>3338121</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
